--- a/daily_matches/job_matches_2026-09-04.xlsx
+++ b/daily_matches/job_matches_2026-09-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Johns Creek, GA, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, XGBoost, Docker, Kubernetes, CI/CD, Git</t>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84f077dc4279aae5</t>
+          <t>https://www.indeed.com/viewjob?jk=f9152e708942be7c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Associate-AI-ML Engineer / GenAI Engineer - Data Scientist</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.1</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Gemini, TensorFlow, PyTorch, Docker, CI/CD</t>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e0a63e3b141bff1</t>
+          <t>https://www.indeed.com/viewjob?jk=c366764337f1ed92</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Generative AI Consultant</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SIA</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>20</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Mistral, Hugging Face, Pinecone, Prompt Engineering, TensorFlow</t>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0395f09e1094e303</t>
+          <t>https://www.indeed.com/viewjob?jk=6058b9b613bca110</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1000000882.DATA ENGINEER II.INFO TECH - OPERATIONS</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dallas County</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>20</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Kinesis, Docker, Kubernetes, CI/CD, Git, Snowflake, Databricks</t>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7843267cf992ea15</t>
+          <t>https://www.indeed.com/viewjob?jk=8f0b2962748d9789</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1000000881.DATA ENGINEER II.INFO TECH - OPERATIONS</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dallas County</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.8</v>
+        <v>20</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Kinesis, Docker, Kubernetes, CI/CD, Git, Snowflake, Databricks</t>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a34457b20435ae3</t>
+          <t>https://www.indeed.com/viewjob?jk=62e526d781156add</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1000000855.AI ENGINEER II.INFO TECH - DATA AND AI</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dallas County</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.8</v>
+        <v>20</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Data Lake, Kinesis, Docker, Kubernetes, CI/CD, Git, Snowflake</t>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,67 +671,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fd77b4f5e4c4be7</t>
+          <t>https://www.indeed.com/viewjob?jk=97bedc8e0921c527</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer - Cloud Infrastructure Automation</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>20</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Pinecone, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cc874ead3887090</t>
+          <t>https://www.indeed.com/viewjob?jk=f053a808a64ce63c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Emerging Risk Strategic Analytics, Senior Associate</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>20</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Python</t>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57b1d499e806f727</t>
+          <t>https://www.indeed.com/viewjob?jk=c2234682221b2376</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>20</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Databricks, Kafka, Hadoop, NoSQL, Python, SQL, R</t>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00be7078de5ae6f7</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2850791f386fd0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>System Engineer, Data Automation and AI</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Moxie Pest Control</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>20</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Prompt Engineering, BigQuery, Apache Airflow, CI/CD, Git, Snowflake, BigQuery, Power BI, Python, SQL</t>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=454c36b233674a1c</t>
+          <t>https://www.indeed.com/viewjob?jk=ea5bd5047cb690b7</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Q2ebanking</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>20</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, Copilot, TensorFlow, PyTorch, Git, Python, R, Java</t>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0266e3da700c828</t>
+          <t>https://www.indeed.com/viewjob?jk=b6c9d895b4b221fc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>20</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, Git, Snowflake, Databricks, PySpark, Tableau, Python, SQL</t>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a88c4ea55f8928b2</t>
+          <t>https://www.indeed.com/viewjob?jk=6f901d63ec543ec6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Enterprise ServiceNow Architect</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>20</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Kafka, R, Scala</t>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e375480799bccd93</t>
+          <t>https://www.indeed.com/viewjob?jk=d7a2c68b1f9879c6</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>20</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Kafka, R, Scala</t>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=533504e307eb3018</t>
+          <t>https://www.indeed.com/viewjob?jk=34cfdf03756d098f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Data Platform Engineer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>20</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Kafka, R, Scala</t>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05ec919a5dec5401</t>
+          <t>https://www.indeed.com/viewjob?jk=3d1deaba387bdf2e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Quality Automation Engineer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>20</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Jenkins, GitHub Actions, Git, Python, SQL, R, Java</t>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b88a93dd5da4536</t>
+          <t>https://www.indeed.com/viewjob?jk=db635ff6ebf1d5ba</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>20</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Prompt Engineering, Git, Python, R, Scala</t>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b95a303a4e0aee7</t>
+          <t>https://www.indeed.com/viewjob?jk=c4df6e348da45185</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Automation Engineer 4 (SDET/API automation)</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>20</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Jenkins, Git, R, Java, Scala</t>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=723a310f2bef935e</t>
+          <t>https://www.indeed.com/viewjob?jk=6493bf4f59fe501c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>20</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Prompt Engineering, Git, Python, R, Scala</t>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f741b12eea513f14</t>
+          <t>https://www.indeed.com/viewjob?jk=0b3b4996f2df17d3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DevSecOps Architect</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hard Rock International</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Davie, FL, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>20</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9dc833901dbedff</t>
+          <t>https://www.indeed.com/viewjob?jk=c769c3d835ff3db7</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Allied Steel Buildings</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>20</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, SQL, R, Scala</t>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb2a14e5409d4e56</t>
+          <t>https://www.indeed.com/viewjob?jk=04781ba0e218324c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior AWS DevOps Engineer - Atlanta</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ImagineX Consulting</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>20</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala, Optimization</t>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bcc0ae4e537f4cc</t>
+          <t>https://www.indeed.com/viewjob?jk=e237f57d26686583</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer III - GenAI Patterns</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>20</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Pinecone, Prompt Engineering, CI/CD, Python, R, Java, Scala</t>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b6197b3bc907d38</t>
+          <t>https://www.indeed.com/viewjob?jk=1d50878a49c11777</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>20</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Jenkins, Terraform, Git, Python, R, Java, Scala</t>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=811249074303b1b7</t>
+          <t>https://www.indeed.com/viewjob?jk=189bcc446c9dab44</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Specialist - Software Engineering</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>20</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Terraform, Git, R, Java, Scala</t>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aac82bb5b3bc86e5</t>
+          <t>https://www.indeed.com/viewjob?jk=44f312befe7b6228</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. QA Engineer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>retail services &amp; systems</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.1</v>
+        <v>20</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java, Scala, Optimization</t>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3156522126b6d94</t>
+          <t>https://www.indeed.com/viewjob?jk=825ced6b050f62ff</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (GitHub Migration Specialist)</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Modus Create</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.1</v>
+        <v>20</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a70046391940aed2</t>
+          <t>https://www.indeed.com/viewjob?jk=bf99c34ea81acf0e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (GitHub Migration Specialist)</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Modus Create</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.1</v>
+        <v>20</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec13bfd98a7dfaf1</t>
+          <t>https://www.indeed.com/viewjob?jk=ca5468b9bf305c96</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior AI Test Automation Engineer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Motion</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.1</v>
+        <v>20</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe4414e4fe56b5fc</t>
+          <t>https://www.indeed.com/viewjob?jk=60f9ca1626e817a0</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, AI Platform</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, PyTorch, Kubernetes, Python, R, Java, Scala</t>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=349542c154ddc955</t>
+          <t>https://www.indeed.com/viewjob?jk=742f43f81b2c60f7</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AI/ML Engineer - Senior Associate</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Kubernetes, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7af4fd0621ffee60</t>
+          <t>https://www.indeed.com/viewjob?jk=2401405eb3baa60e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e021c7f064107aed</t>
+          <t>https://www.indeed.com/viewjob?jk=745d572a1734deb3</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Resident Solutions Architects / Forward Deployed Engineers</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>TANGENTTECH</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RAG, MLflow, CI/CD, Databricks, Python, SQL, R, Scala, Optimization</t>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=091ab5f176355651</t>
+          <t>https://www.indeed.com/viewjob?jk=86fa80072663c39c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Specialist - Software Engineering</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Pennington, NJ, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, R, Java, Scala</t>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46314e136a4f49dc</t>
+          <t>https://www.indeed.com/viewjob?jk=34becb3bb737a3a8</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medina Talent Group </t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RAG, S3, Kubernetes, CI/CD, Git, Kafka, MongoDB, Python, R</t>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fff0bfc557ef716</t>
+          <t>https://www.indeed.com/viewjob?jk=40c481cde165be31</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,42 +1721,1862 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbfe2ba73ed1707</t>
+          <t>https://www.indeed.com/viewjob?jk=d3246b068fda8b24</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Applied AI Technologist</t>
+          <t>Senior Full-Stack Developer - AI</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SixSpeed</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
+        <v>20</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=01a11e4dca1338bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>20</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=19cafaf0905d6ccd</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CO, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>20</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d179f64661459840</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>WV, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>20</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=927f4de3ddcabe55</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>SC, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>20</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=55c467b89913b40c</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>MI, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>20</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=97f79742bd18fbf9</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>20</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=48534502200da502</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>MN, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>20</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2ce4e192219a234</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>MT, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>20</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c386ab65035eb143</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>MS, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>20</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=38959fe002eaa620</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ID, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>20</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c5a45ce59fb7c995</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Developer - AI</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NV, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>20</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9c332f08ebbb5911</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>DataBricks Data Engineer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Prodapt Solutions</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Synapse, Data Lake, CI/CD, Terraform, Git, Snowflake, Databricks, PySpark</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8575f37d6f1acd78</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Sr. Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Ford Motor Company</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Dearborn, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, NoSQL</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f91a79069b7b6c23</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Rakuten International</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>San Mateo, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, FastAPI, Docker, CI/CD, GitHub Actions, Git, Kafka, PostgreSQL, MySQL</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b44a19f12a8e8842</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Sr. AI/Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Intellivo</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Memphis, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Mistral, TensorFlow, PyTorch, XGBoost, Azure ML</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=93a647a90dbe7e6a</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer I</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Tandem Diabetes Care, Inc.</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Milan, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kinesis, Docker, Kubernetes, CI/CD, Git, Kafka, MySQL, MongoDB</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31ff8701b147ac9f</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer - AI Quality and Productivity</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Warren, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Databricks, PostgreSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d251da15ad981a86</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Data Scientist II, New College Grad- Master's (Santa Clara, CA)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Applied Materials</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, BigQuery, Snowflake, Databricks, BigQuery, Tableau, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a8bc8442250535cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Sourceo</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>IN, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Docker, Kubernetes, Git, Databricks, Kafka, Power BI, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a95571cda13f4ac4</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Senior Platform Software Engineer</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Kubernetes, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da7bf576857a8aca</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Senior Platform Software Engineer</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Kubernetes, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d4beb6556e233fc4</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Senior Platform Software Engineer</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Kubernetes, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=06e5b9997367f58a</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, PyTorch, S3, Kubernetes, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64cd138edc42e2e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Applied AI Science Co-op - Embedding models and Personalization</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Ancestry</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Keras, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a91337af49c1bc76</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Java Full Stack Developer-Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, Kafka, MongoDB, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=32ae9d63b93b018e</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Sr Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Alight Solutions</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Git, Tableau, Power BI, Quicksight, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7e3c21146bb634f</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist, Defect Quality &amp; Systems</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Samsung Electronics</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
         <v>10</v>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Git, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=136cbc2e0cdc3fef</t>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, FastAPI, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e36313756d15747</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, S3, CI/CD, Jenkins, Git, R, Java</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ea947be91c507fb0</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer II - Risk</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Aledade</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=59fcd712375ba35e</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Marketing Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Ericsson</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>RAG, Cortex, CI/CD, Snowflake, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b9f2e4569d1db6a</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Marketing Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Ericsson</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>RAG, Cortex, CI/CD, Snowflake, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0d84c664bc28f4ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Park Place Technologies</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Highland Heights, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Data Scientist, Azure ML, Synapse, Data Lake, Git, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2036be33a66f5172</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Data Scientist - Product Safety Data Analytics</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Warren, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8d762c0ce05fb2ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=08a841005a79bd72</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24d9675817a64cf7</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53d37910dc7c5a1f</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c30155937f66ae41</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bd94dbb79d7abcc9</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8066d79c18e6e5e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Jericho, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b82d1cd07bc3c3c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c6992b10693e1a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b8f72f7afebf5df4</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ea9aa357310f0a0b</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Princeton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e8292528ac6ce40</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=397c5ed0ca7d58e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=845397acd7122aed</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Omaha, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=89fe0814325c110f</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=428a651cf3335a8e</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e48124941694bc3a</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57bc16540033886c</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d5e58b53ffb80f56</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1dad71d0c9341bd3</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-09-04.xlsx
+++ b/daily_matches/job_matches_2026-09-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Engineer - Direct Hire Only, no Corp-2-Corp</t>
+          <t>Software Engineer (Python, Java, C++, or GoLang) - Chicago, IL- ONSITE 2X Week- FreeWheel</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pistevo Decision</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.4</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, S3, Docker, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b60fbf6be4c551ad</t>
+          <t>https://www.indeed.com/viewjob?jk=e0cea54622c0ce7d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI/ML Engineer Precision Oncology</t>
+          <t>Generative AI Engineer (4-5 Years Experience)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Moffitt Cancer Center</t>
+          <t>Verveba telecom</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Hugging Face, PyTorch, CI/CD, Git, Python, R</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Pinecone, TensorFlow, PyTorch, Keras, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,59 +531,59 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8db73b8028284c06</t>
+          <t>https://www.indeed.com/viewjob?jk=ae5981c488755ac7</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI/ML Engineer Precision Oncology</t>
+          <t>Data Engineer (DataLake to AWS)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Moffitt Cancer Center</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Hugging Face, PyTorch, CI/CD, Git, Python, R</t>
+          <t>RAG, Kubernetes, CI/CD, Git, Snowflake, Kafka, Hadoop, Python, SQL, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28fada676edd1a21</t>
+          <t>https://www.indeed.com/viewjob?jk=7fa01137fb1dea76</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AI &amp; Agents</t>
+          <t>Gen AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Appnovation Technologies</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Cortex, S3, Apache Airflow, CI/CD, Git, Snowflake, Databricks, PySpark, Python</t>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3734453d62a91f7</t>
+          <t>https://www.indeed.com/viewjob?jk=df0deb6fd9e533ca</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AI &amp; Agents</t>
+          <t>Sr. Analyst, Supply Chain Data Analytics</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Appnovation Technologies</t>
+          <t>Newell Brands</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Cortex, S3, Apache Airflow, CI/CD, Git, Snowflake, Databricks, PySpark, Python</t>
+          <t>AI Engineer, RAG, Copilot, Git, Databricks, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c63f982e3b90ae6e</t>
+          <t>https://www.indeed.com/viewjob?jk=3e56e79b023c480f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AI &amp; Agents</t>
+          <t>Applications Engineer - Senior</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Appnovation Technologies</t>
+          <t>NOVON Consulting</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Cortex, S3, Apache Airflow, CI/CD, Git, Snowflake, Databricks, PySpark, Python</t>
+          <t>AI Engineer, Generative AI, RAG, Gemini, Prompt Engineering, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8428fb5228d600</t>
+          <t>https://www.indeed.com/viewjob?jk=df34afb40bf5c4cf</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer Sr - Pega Developer</t>
+          <t>Senior Python Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>EPAM Systems</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, CI/CD, Jenkins, Git, PostgreSQL, SQL, R, Java, Scala</t>
+          <t>Copilot, Data Lake, FastAPI, Terraform, Git, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e30a25501a39a5f1</t>
+          <t>https://www.indeed.com/viewjob?jk=8471609834aa2a27</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>USA - Tax - BTS - FTA - EDGE STEM R&amp;D Credits - Technology - Intern - Summer 2027</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Copilot, Docker, CI/CD, Git, Snowflake, Databricks, Kafka, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Copilot, AKS, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a155cddb69c0b0</t>
+          <t>https://www.indeed.com/viewjob?jk=77c40be597a87b3b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Generative AI Engineer (2-3 Years Experience)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Aureon</t>
+          <t>Verveba telecom</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, CI/CD, Databricks, Power BI, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=761ae4e0fd8c073b</t>
+          <t>https://www.indeed.com/viewjob?jk=24071b98c910bce8</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Data Engineering Intern</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Innovation Associates, Inc.</t>
+          <t>Amdocs</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Binghamton, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,42 +801,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, Data Lake, Databricks, Tableau, Power BI, Python, SQL, R, Java, Scala</t>
+          <t>LangChain, RAG, Databricks, PySpark, PostgreSQL, MongoDB, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2ea5af3859d76d5</t>
+          <t>https://www.indeed.com/viewjob?jk=0896e0a6d30f4222</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer - Office-Based in Minnesota</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>UnitedHealth Group</t>
+          <t>Rhombus Power</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Lake, CI/CD, Git, Snowflake, Databricks, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8abd386f3997679</t>
+          <t>https://www.indeed.com/viewjob?jk=bec097fb7f2babaa</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>USA - Tax - Tax Technology and Transformation (TTT) - FSO - Technology Advisory - Intern - Summer 20</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Gap Inc.</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,17 +871,157 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, AWS SageMaker, Azure ML, Databricks, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, Copilot, AKS, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a7e8caf8e6ee509</t>
+          <t>https://www.indeed.com/viewjob?jk=e51f1592a2558dd2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>USA - Tax - Tax Technology and Transformation (TTT) - FSO - Technology Advisory - Analyst</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>EY</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, AKS, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=73afea5935ba12be</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>FanDuel</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Data Scientist, CI/CD, Databricks, Kafka, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34f903a4cd4deb68</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>USA - Tax - Tax Technology and Transformation (TTT) - Artificial Intelligence - Intern - Summer 2027</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>EY</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, AKS, Git, Snowflake, Databricks, Python, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c0ee3eca93d56ae6</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>USA - Tax - Tax Technology and Transformation (TTT) - Artificial Intelligence - Analyst</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>EY</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, AKS, Git, Snowflake, Databricks, Python, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f5fbab2f518f237</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-09-04.xlsx
+++ b/daily_matches/job_matches_2026-09-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer (Python, Java, C++, or GoLang) - Chicago, IL- ONSITE 2X Week- FreeWheel</t>
+          <t>Sr. Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Persistent Systems</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake, Databricks</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Mistral, Hugging Face, FAISS, Pinecone</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0cea54622c0ce7d</t>
+          <t>https://www.indeed.com/viewjob?jk=d07f9859bf5d647a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generative AI Engineer (4-5 Years Experience)</t>
+          <t>Software Engineer, II - Data Engineering</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Verveba telecom</t>
+          <t>TORC Robotics</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Pinecone, TensorFlow, PyTorch, Keras, Python</t>
+          <t>RAG, Glue, Athena, Data Lake, Docker, Apache Airflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae5981c488755ac7</t>
+          <t>https://www.indeed.com/viewjob?jk=2aeb88d99c11a926</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer (DataLake to AWS)</t>
+          <t>Backend Java Developer, Officer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Git, Snowflake, Kafka, Hadoop, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Jenkins, Git, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fa01137fb1dea76</t>
+          <t>https://www.indeed.com/viewjob?jk=62cd96fe08a5ed3c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Gen AI Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Wyoming, MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, Python, SQL</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, BigQuery, Docker, Kubernetes, CI/CD, Terraform, Git, BigQuery</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df0deb6fd9e533ca</t>
+          <t>https://www.indeed.com/viewjob?jk=639ed0412b5015c8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Analyst, Supply Chain Data Analytics</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Newell Brands</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Git, Databricks, Tableau, Power BI, Python, SQL, R</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Kubernetes</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e56e79b023c480f</t>
+          <t>https://www.indeed.com/viewjob?jk=0e388bf27c0990b1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Applications Engineer - Senior</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NOVON Consulting</t>
+          <t>Pattern</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Gemini, Prompt Engineering, Git, Python, SQL, R, Java</t>
+          <t>Data Scientist, RAG, S3, Glue, Kubernetes, CI/CD, Terraform, Snowflake, Databricks, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df34afb40bf5c4cf</t>
+          <t>https://www.indeed.com/viewjob?jk=84bee97389b15764</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Python Engineer</t>
+          <t>Data Warehouse &amp; Analytics Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EPAM Systems</t>
+          <t>Virtru</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Copilot, Data Lake, FastAPI, Terraform, Git, NoSQL, Python, SQL, R, Scala</t>
+          <t>RAG, Redshift, BigQuery, Synapse, Data Lake, Kubernetes, CI/CD, Terraform, Git, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8471609834aa2a27</t>
+          <t>https://www.indeed.com/viewjob?jk=18ffdd5eef1958d3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>USA - Tax - BTS - FTA - EDGE STEM R&amp;D Credits - Technology - Intern - Summer 2027</t>
+          <t>Data Warehouse &amp; Analytics Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Virtru</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, AKS, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, Redshift, BigQuery, Synapse, Data Lake, Kubernetes, CI/CD, Terraform, Git, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77c40be597a87b3b</t>
+          <t>https://www.indeed.com/viewjob?jk=c7452d97c75af8dc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Generative AI Engineer (2-3 Years Experience)</t>
+          <t>Data Warehouse &amp; Analytics Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Verveba telecom</t>
+          <t>Virtru</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Python, R, Optimization</t>
+          <t>RAG, Redshift, BigQuery, Synapse, Data Lake, Kubernetes, CI/CD, Terraform, Git, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24071b98c910bce8</t>
+          <t>https://www.indeed.com/viewjob?jk=f0020bbdb6ae8cba</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Warehouse &amp; Analytics Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Amdocs</t>
+          <t>Virtru</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Databricks, PySpark, PostgreSQL, MongoDB, Python, SQL, R, Scala</t>
+          <t>RAG, Redshift, BigQuery, Synapse, Data Lake, Kubernetes, CI/CD, Terraform, Git, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0896e0a6d30f4222</t>
+          <t>https://www.indeed.com/viewjob?jk=69f9a0ce557bd0b4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Warehouse &amp; Analytics Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rhombus Power</t>
+          <t>Virtru</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R</t>
+          <t>RAG, Redshift, BigQuery, Synapse, Data Lake, Kubernetes, CI/CD, Terraform, Git, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bec097fb7f2babaa</t>
+          <t>https://www.indeed.com/viewjob?jk=b00da2a69a1c8752</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>USA - Tax - Tax Technology and Transformation (TTT) - FSO - Technology Advisory - Intern - Summer 20</t>
+          <t>Data Warehouse &amp; Analytics Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Virtru</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, AKS, Git, Python, SQL, R, Java</t>
+          <t>RAG, Redshift, BigQuery, Synapse, Data Lake, Kubernetes, CI/CD, Terraform, Git, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e51f1592a2558dd2</t>
+          <t>https://www.indeed.com/viewjob?jk=2da011c549fe5788</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>USA - Tax - Tax Technology and Transformation (TTT) - FSO - Technology Advisory - Analyst</t>
+          <t>Data Warehouse &amp; Analytics Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Virtru</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, AKS, Git, Python, SQL, R, Java</t>
+          <t>RAG, Redshift, BigQuery, Synapse, Data Lake, Kubernetes, CI/CD, Terraform, Git, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73afea5935ba12be</t>
+          <t>https://www.indeed.com/viewjob?jk=c5ee9bf2ddf6f37b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer Consultant II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, CI/CD, Databricks, Kafka, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Jenkins, Git, PostgreSQL, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34f903a4cd4deb68</t>
+          <t>https://www.indeed.com/viewjob?jk=a34c6d42c8ceedf1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>USA - Tax - Tax Technology and Transformation (TTT) - Artificial Intelligence - Intern - Summer 2027</t>
+          <t>Quality Engineer (AI Automation)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Teaneck, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, AKS, Git, Snowflake, Databricks, Python, R</t>
+          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,42 +986,1722 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0ee3eca93d56ae6</t>
+          <t>https://www.indeed.com/viewjob?jk=e3f2f5926f656008</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>USA - Tax - Tax Technology and Transformation (TTT) - Artificial Intelligence - Analyst</t>
+          <t>Quality Engineer (AI Automation)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>Teaneck, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b1d4adb068d62e2d</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Quality Engineer (AI Automation)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Teaneck, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e675cdcd96b332e</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Quality Engineer (AI Automation)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Teaneck, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=72eb919c1569115c</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Quality Engineer (AI Automation)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Teaneck, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=131146cc601fd7d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Quality Engineer (AI Automation)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Teaneck, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fbfb4849ddd220f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Quality Engineer (AI Automation)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Teaneck, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=820cd96de02dab88</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Quality Engineer (AI Automation)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Teaneck, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4dd0fc0a61a4a2ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Quality Engineer (AI Automation)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Teaneck, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8ecd5881099b9b5e</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Quality Engineer (AI Automation)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Teaneck, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ade4a54efa6d9ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Quality Engineer (AI Automation)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Teaneck, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5960457c0c59b0bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Quality Engineer (AI Automation)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Teaneck, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b032b294317bab4</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Data Engineer, AI &amp; Business Intelligence- San Diego</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Event Network, LLC</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, CI/CD, Terraform, Git, Databricks, Power BI, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b557bb2570f0fa65</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>AI &amp; Data Scientist Intern</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Ingredion</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Westchester, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Git, Hadoop, NoSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f397c0a18bd345db</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Sr. Data Scientist - Remote</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Minnetonka, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, Git, Snowflake, Databricks, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0fe315c9891ef44a</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Software Engineer IV, Datastore</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Beacon Biosignals</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Kinesis, Kubernetes, Terraform, Git, Kafka, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f0c95a6345870500</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Gen AI Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Batch Systems Inc</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Sherman Oaks, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8cde3ee710708311</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Software Engineer III (Java/Python/AWS)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, Kafka, PostgreSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c218f1db2c299ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior AI Java Developer - TX</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Baanyan Software Services Inc.</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Texas City, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Gemini, Copilot, Prompt Engineering, CI/CD, Git, Kafka, PostgreSQL, MongoDB, SQL, R</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b64d84452c0995bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst - Operations (Agency Temp)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SCAN Health Plan</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Long Beach, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Cortex, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f167bbc49ae998e2</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Data Scientist, Merchandising Analytics</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Tractor Supply</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Brentwood, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Databricks, PySpark, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=79d99ef5885c9adc</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senior AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, S3, Athena, Git, Snowflake, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=91930a30f0def5b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Dynamic Lifecycle Innovations</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Milwaukee, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, Databricks, PySpark, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e0019cb84ac3bc92</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Dynamic Lifecycle Innovations</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, Databricks, PySpark, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=66c47c01ec242b5c</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Dynamic Lifecycle Innovations</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, Databricks, PySpark, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=be4df5dec943b09f</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Software Developer III - Cloud Platform (Back End, Authentication)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>National Information Solutions Cooperative (NISC)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Docker, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ad901d7053c9abd</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Summer 2027 Generative AI Internship</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Nationwide Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, R</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd292d7cd2903a25</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Senior Analyst</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Trustly</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
           <t>New York, NY, US USA</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D43" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Tableau, Power BI, Python, SQL, R, Scala, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b68682989110241</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>AI Applications Engineer</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ARNOLD &amp; PORTER LLP</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=945a18892022dd9d</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Senior Business Intelligence &amp; Automation Analyst</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>McKesson</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
         <v>10</v>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, AKS, Git, Snowflake, Databricks, Python, R</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6f5fbab2f518f237</t>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>RAG, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab114b4702aecc56</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Medical Coding Implementation Engineer</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Commence</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=68f0e856c9963690</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Summer 2027 Feature Engineer Internship</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Nationwide Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, Git, Snowflake, Databricks, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e0b2625c0479d624</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Allegiant Air</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>S3, Glue, Redshift, Terraform, Redshift, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afbb890dc03e6cf2</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Koch</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0d01a9a738904def</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Koch</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=799e930d22594edb</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Koch</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Wichita, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=701ad5e918c0a3e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Data Engineer I (Full-Time) - United States</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Research Triangle Park, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>RAG, Git, Hadoop, PostgreSQL, MySQL, MongoDB, Tableau, SQL, R</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4c4c2eb2aae26e36</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Power Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Red Thread</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Git, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c116d7172dfca925</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Flexential</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d5b6600f4a52433b</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>HumanSignal</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, Kubernetes, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d2d444c7605271a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>HumanSignal</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, Kubernetes, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=02fa6dc280a03eed</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Function Health</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Git, Databricks, Dask, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4a5a9bb41629960</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>AI Engineering Intern (Summer 2027)</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Bain &amp; Company</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Copilot, CI/CD, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4f7fbcc948ca9d51</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Lyft</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Python, R, Optimization, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=979c6e5202e2ed80</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Lyft</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Python, R, Optimization, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9535ab66048eb340</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist, Marketing</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>The Home Depot</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c9842da8e43af9b</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Data Scientist, Fraud Risk</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Imprint</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2f3a8371608ec1e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Data Scientist, Fraud Risk</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Imprint</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=294e2921c67effba</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Data Scientist, Fraud Risk</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Imprint</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b511c66f079f86cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Data Science Intern</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>QBE</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Madison, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, MLflow, FastAPI, Docker, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=05d2ba3327e40ba0</t>
         </is>
       </c>
     </row>
